--- a/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_generator_bearings_clustering/clustering/dsas_g11_generator_bearings/clustering_g11_generator_bearings_output4.xlsx
+++ b/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_generator_bearings_clustering/clustering/dsas_g11_generator_bearings/clustering_g11_generator_bearings_output4.xlsx
@@ -656,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.701487338215738</v>
+        <v>1.701487338215736</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.769245399025623</v>
+        <v>1.769245399025622</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.805122053582846</v>
+        <v>1.805122053582845</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.801061817704851</v>
+        <v>1.801061817704849</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.837194489361635</v>
+        <v>1.837194489361633</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.860470559391944</v>
+        <v>1.860470559391942</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.909011251222491</v>
+        <v>1.909011251222489</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.818202629194581</v>
+        <v>1.81820262919458</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.867295527014036</v>
+        <v>1.867295527014035</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.882128559497732</v>
+        <v>1.882128559497731</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.982636074972178</v>
+        <v>1.982636074972177</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.024993125128094</v>
+        <v>2.024993125128093</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.166437668984746</v>
+        <v>2.166437668984745</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.121302309973909</v>
+        <v>2.121302309973908</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.117646873789523</v>
+        <v>2.117646873789521</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.018200939540431</v>
+        <v>2.01820093954043</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.042502742371339</v>
+        <v>2.042502742371338</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.069149405370396</v>
+        <v>2.069149405370395</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.062064448942767</v>
+        <v>2.062064448942766</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.028398914334054</v>
+        <v>2.028398914334053</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.029726819916946</v>
+        <v>2.029726819916945</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.976776360740485</v>
+        <v>1.976776360740484</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.937147343696977</v>
+        <v>1.937147343696976</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.754287536768283</v>
+        <v>1.754287536768284</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.812346381967397</v>
+        <v>1.812346381967398</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.686110633523834</v>
+        <v>1.686110633523833</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>1</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.688302286336887</v>
+        <v>1.688302286336886</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.657373543320254</v>
+        <v>1.657373543320253</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.734770456189486</v>
+        <v>1.734770456189485</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.646498072617438</v>
+        <v>1.646498072617437</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.644332472907881</v>
+        <v>1.644332472907879</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.663231182623765</v>
+        <v>1.663231182623764</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>1</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.700822597242067</v>
+        <v>1.700822597242065</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.694094533775351</v>
+        <v>1.694094533775349</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.660882453136852</v>
+        <v>1.660882453136851</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.567522940196401</v>
+        <v>1.5675229401964</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.621490111271075</v>
+        <v>1.621490111271074</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.596123302501045</v>
+        <v>1.596123302501044</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.684307349447264</v>
+        <v>1.684307349447263</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.577057919781328</v>
+        <v>1.577057919781329</v>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>1</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.766026090597252</v>
+        <v>1.766026090597253</v>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.792772835846816</v>
+        <v>1.792772835846817</v>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.838748349291137</v>
+        <v>1.838748349291138</v>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.806266056738922</v>
+        <v>1.806266056738923</v>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>1</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.69692670540638</v>
+        <v>1.696926705406379</v>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>1</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.680413698200781</v>
+        <v>1.68041369820078</v>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>1</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.64513801706041</v>
+        <v>1.645138017060409</v>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.667176725157446</v>
+        <v>1.667176725157445</v>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.702360787753061</v>
+        <v>1.70236078775306</v>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.594859512986724</v>
+        <v>1.594859512986723</v>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>1</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.676046807305354</v>
+        <v>1.676046807305355</v>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>1</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.791055737829681</v>
+        <v>1.791055737829682</v>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>1</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.641825796581885</v>
+        <v>1.641825796581884</v>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>1</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.608329539326732</v>
+        <v>1.608329539326731</v>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>1</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.483659717945441</v>
+        <v>1.48365971794544</v>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.500582601637044</v>
+        <v>1.500582601637043</v>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>1</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.497631773930219</v>
+        <v>1.497631773930218</v>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>1</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.575626232082915</v>
+        <v>1.575626232082914</v>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>1</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.610249485456368</v>
+        <v>1.610249485456367</v>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>1</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.711960663567124</v>
+        <v>1.711960663567123</v>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>1</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.64097744604709</v>
+        <v>1.640977446047089</v>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>1</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.683090650942806</v>
+        <v>1.683090650942805</v>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>1</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.743272208553963</v>
+        <v>1.743272208553962</v>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>1</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.824521801981437</v>
+        <v>1.824521801981436</v>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.740207009483759</v>
+        <v>1.740207009483758</v>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.711525420679671</v>
+        <v>1.71152542067967</v>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>1</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.629646609854662</v>
+        <v>1.62964660985466</v>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>1</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.532521021904885</v>
+        <v>1.532521021904884</v>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.483052850409726</v>
+        <v>1.483052850409724</v>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.526626790864768</v>
+        <v>1.526626790864767</v>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>1</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.506062538200872</v>
+        <v>1.506062538200871</v>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>1</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.498807757489673</v>
+        <v>1.498807757489672</v>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>1</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.502618561004059</v>
+        <v>1.502618561004058</v>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>1</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.538789178658807</v>
+        <v>1.538789178658806</v>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>1</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.545211739938707</v>
+        <v>1.545211739938706</v>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>1</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.555963015227174</v>
+        <v>1.555963015227173</v>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.527165499068889</v>
+        <v>1.527165499068888</v>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>1</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.473636600044063</v>
+        <v>1.473636600044062</v>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.479268451140706</v>
+        <v>1.479268451140705</v>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>1</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.568835565829017</v>
+        <v>1.568835565829016</v>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>1</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.650491714979714</v>
+        <v>1.650491714979712</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>1</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.698362620133469</v>
+        <v>1.698362620133467</v>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>1</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.734828641735721</v>
+        <v>1.734828641735719</v>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>1</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.746065943517971</v>
+        <v>1.74606594351797</v>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>1</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.702477638103336</v>
+        <v>1.702477638103335</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>1</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.730730757300258</v>
+        <v>1.730730757300257</v>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>1</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.815185706232127</v>
+        <v>1.815185706232125</v>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>1</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.871241577124708</v>
+        <v>1.871241577124706</v>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>1</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.73333082692236</v>
+        <v>1.733330826922358</v>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>1</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.554437563317749</v>
+        <v>1.554437563317748</v>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>1</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.589770709756862</v>
+        <v>1.589770709756863</v>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>1</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.615104404461</v>
+        <v>1.615104404461001</v>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>1</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.705552719460296</v>
+        <v>1.705552719460297</v>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>1</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.655748919563923</v>
+        <v>1.655748919563922</v>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>1</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.651041541933053</v>
+        <v>1.651041541933052</v>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>1</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.680738137558452</v>
+        <v>1.680738137558451</v>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>1</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.52859547344998</v>
+        <v>1.528595473449979</v>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>1</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.508833626567259</v>
+        <v>1.508833626567258</v>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>1</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.490441917783151</v>
+        <v>1.49044191778315</v>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>1</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.880579122237398</v>
+        <v>1.880579122237399</v>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>1</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.999155014638111</v>
+        <v>1.999155014638112</v>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>1</v>
       </c>
       <c r="AA136" t="n">
-        <v>2.118319061576189</v>
+        <v>2.11831906157619</v>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>1</v>
       </c>
       <c r="AA137" t="n">
-        <v>2.313315606300594</v>
+        <v>2.313315606300595</v>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>1</v>
       </c>
       <c r="AA140" t="n">
-        <v>2.129641904069936</v>
+        <v>2.129641904069937</v>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>1</v>
       </c>
       <c r="AA141" t="n">
-        <v>2.119437486207662</v>
+        <v>2.119437486207664</v>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>1</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.983803318534164</v>
+        <v>1.983803318534166</v>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>1</v>
       </c>
       <c r="AA143" t="n">
-        <v>2.030709705728039</v>
+        <v>2.03070970572804</v>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>1</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.723189247168214</v>
+        <v>1.723189247168215</v>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>1</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.757327229678469</v>
+        <v>1.75732722967847</v>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>2</v>
       </c>
       <c r="AA149" t="n">
-        <v>2.708521991415318</v>
+        <v>2.708521991415319</v>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>2</v>
       </c>
       <c r="AA150" t="n">
-        <v>2.669476821147224</v>
+        <v>2.669476821147226</v>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>2</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.705096044275254</v>
+        <v>2.705096044275255</v>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>1</v>
       </c>
       <c r="AA152" t="n">
-        <v>2.060254065672829</v>
+        <v>2.06025406567283</v>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>1</v>
       </c>
       <c r="AA153" t="n">
-        <v>2.184634020117052</v>
+        <v>2.184634020117055</v>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>1</v>
       </c>
       <c r="AA154" t="n">
-        <v>2.199729350492553</v>
+        <v>2.199729350492555</v>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>1</v>
       </c>
       <c r="AA155" t="n">
-        <v>2.258152068404049</v>
+        <v>2.258152068404051</v>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>1</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.821603479879031</v>
+        <v>1.821603479879032</v>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>1</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.845917801683855</v>
+        <v>1.845917801683856</v>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>1</v>
       </c>
       <c r="AA158" t="n">
-        <v>2.300049743811994</v>
+        <v>2.300049743811996</v>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>1</v>
       </c>
       <c r="AA159" t="n">
-        <v>2.508482895796311</v>
+        <v>2.508482895796313</v>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>1</v>
       </c>
       <c r="AA160" t="n">
-        <v>2.609196584180836</v>
+        <v>2.609196584180838</v>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>1</v>
       </c>
       <c r="AA161" t="n">
-        <v>2.665318303192652</v>
+        <v>2.665318303192654</v>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>1</v>
       </c>
       <c r="AA162" t="n">
-        <v>2.064964922003802</v>
+        <v>2.064964922003804</v>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>1</v>
       </c>
       <c r="AA163" t="n">
-        <v>2.062038037067734</v>
+        <v>2.062038037067735</v>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>1</v>
       </c>
       <c r="AA164" t="n">
-        <v>2.561316457454028</v>
+        <v>2.56131645745403</v>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>1</v>
       </c>
       <c r="AA165" t="n">
-        <v>2.66874418061699</v>
+        <v>2.668744180616992</v>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>1</v>
       </c>
       <c r="AA166" t="n">
-        <v>2.702742014144543</v>
+        <v>2.702742014144544</v>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>1</v>
       </c>
       <c r="AA167" t="n">
-        <v>2.712920806198019</v>
+        <v>2.712920806198021</v>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>1</v>
       </c>
       <c r="AA168" t="n">
-        <v>2.030449079132775</v>
+        <v>2.030449079132776</v>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>1</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.934755637521584</v>
+        <v>1.934755637521585</v>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>1</v>
       </c>
       <c r="AA170" t="n">
-        <v>2.152790039946558</v>
+        <v>2.152790039946559</v>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>1</v>
       </c>
       <c r="AA171" t="n">
-        <v>2.21040117686049</v>
+        <v>2.210401176860492</v>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AA172" t="n">
-        <v>2.231665759730315</v>
+        <v>2.231665759730316</v>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>1</v>
       </c>
       <c r="AA173" t="n">
-        <v>2.287787410374459</v>
+        <v>2.28778741037446</v>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>1</v>
       </c>
       <c r="AA176" t="n">
-        <v>2.026541664331614</v>
+        <v>2.026541664331615</v>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>1</v>
       </c>
       <c r="AA177" t="n">
-        <v>2.084749749884583</v>
+        <v>2.084749749884584</v>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>1</v>
       </c>
       <c r="AA178" t="n">
-        <v>2.155217594995146</v>
+        <v>2.155217594995147</v>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
